--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bondlend/TrdBondLendTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bondlend/TrdBondLendTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>交易编号</t>
   </si>
@@ -39,16 +39,13 @@
     <t>交易类型</t>
   </si>
   <si>
-    <t>交易日</t>
-  </si>
-  <si>
-    <t>交割日</t>
-  </si>
-  <si>
-    <t>起息日</t>
-  </si>
-  <si>
-    <t>到期日</t>
+    <t>交易日期</t>
+  </si>
+  <si>
+    <t>首次结算日</t>
+  </si>
+  <si>
+    <t>到期结算日</t>
   </si>
   <si>
     <t>借贷期限</t>
@@ -61,9 +58,6 @@
   </si>
   <si>
     <t>借贷费用</t>
-  </si>
-  <si>
-    <t>结算金额</t>
   </si>
   <si>
     <t>币种</t>
@@ -77,9 +71,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
@@ -98,69 +92,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -172,9 +108,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -182,22 +124,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,17 +153,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,7 +193,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,181 +245,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,26 +439,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -499,15 +478,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -519,6 +489,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,6 +522,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -548,10 +542,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,133 +554,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1051,7 +1045,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
@@ -1062,19 +1056,17 @@
     <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="16.7666666666667" customWidth="1"/>
     <col min="8" max="8" width="13.2583333333333" customWidth="1"/>
-    <col min="9" max="9" width="13" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.8416666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.3416666666667" customWidth="1"/>
-    <col min="12" max="12" width="12.3833333333333" customWidth="1"/>
-    <col min="13" max="13" width="17.425" customWidth="1"/>
-    <col min="14" max="14" width="12.3833333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.1333333333333" customWidth="1"/>
-    <col min="16" max="16" width="9.20833333333333" customWidth="1"/>
-    <col min="17" max="17" width="12.3833333333333" customWidth="1"/>
-    <col min="18" max="18" width="14.575" customWidth="1"/>
+    <col min="9" max="9" width="11.8416666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.3416666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.3833333333333" customWidth="1"/>
+    <col min="12" max="12" width="17.425" customWidth="1"/>
+    <col min="13" max="13" width="12.3833333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.1333333333333" customWidth="1"/>
+    <col min="15" max="15" width="17.2083333333333" customWidth="1"/>
+    <col min="16" max="16" width="14.575" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1091,7 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -1122,12 +1114,6 @@
       </c>
       <c r="P1" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
